--- a/wella/productos.xlsx
+++ b/wella/productos.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evazquez\Desktop\form con precios\wella\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evazquez\Desktop\PEDIDOS ARIMEX ONLINE OK\wella\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="159">
   <si>
     <t>Familia</t>
   </si>
@@ -284,132 +284,6 @@
     <t xml:space="preserve">WP Nutri-Enrich Booster 100 ml </t>
   </si>
   <si>
-    <t>Seb Dark Oil Multivitaminas</t>
-  </si>
-  <si>
-    <t>Seb Dark oil Shampoo 1000 ml</t>
-  </si>
-  <si>
-    <t>Seb Dark oil Conditioner 1000 ml</t>
-  </si>
-  <si>
-    <t>Seb Dark oil Mask 500 ml</t>
-  </si>
-  <si>
-    <t>Seb Dark oil Shampoo 250 ml</t>
-  </si>
-  <si>
-    <t>Seb Dark oil Conditioner 250 ml</t>
-  </si>
-  <si>
-    <t>Seb Dark oil Treatment 250 ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seb Hydre Shampoo 1000ml </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seb Hydre Conditioner 1000ml </t>
-  </si>
-  <si>
-    <t>Seb Hydre PRO Treatment  500ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seb Hydre Shampoo 250ml </t>
-  </si>
-  <si>
-    <t>Seb Hydre Conditioner 250ml</t>
-  </si>
-  <si>
-    <t>Seb Hydre Treatment 150ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seb Penetraitt Shampoo 1000ml </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seb Penetraitt Condition 1000ml </t>
-  </si>
-  <si>
-    <t>Seb Penetraitt PRO Masque 500ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seb Penetraitt Shampoo 250ml </t>
-  </si>
-  <si>
-    <t>Seb Penetraitt Condition 250ml</t>
-  </si>
-  <si>
-    <t>Seb Penetraitt Masque 150ml</t>
-  </si>
-  <si>
-    <t>Seb trilliance Shampoo 1000ml</t>
-  </si>
-  <si>
-    <t>Seb trilliance Conditioner 1000ml</t>
-  </si>
-  <si>
-    <t>Seb Trilliance Shampoo 250ml</t>
-  </si>
-  <si>
-    <t>Seb Trilliance Conditioner 250ml</t>
-  </si>
-  <si>
-    <t>Sebastian Curl Shampoo 1000ml Multilang</t>
-  </si>
-  <si>
-    <t>Sebastian Curl Mask 500ml Multilang</t>
-  </si>
-  <si>
-    <t>Sebastian Curl Shampoo 250ml Multilang</t>
-  </si>
-  <si>
-    <t>Sebastian Curl Cond 250ml Multilang</t>
-  </si>
-  <si>
-    <t>Sebastian Curl Mask 150ml WE_Multilang</t>
-  </si>
-  <si>
-    <t>Sebastian Curl Cream 145ml WE_Multilang</t>
-  </si>
-  <si>
-    <t>Sebastian Curl Foam 200ml ESPTSCAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seb Craft Clay Remold 50ml </t>
-  </si>
-  <si>
-    <t>Seb Matte Putty Soft</t>
-  </si>
-  <si>
-    <t>Seb Liquid Steel Styler</t>
-  </si>
-  <si>
-    <t>Seb Texturizer Gel</t>
-  </si>
-  <si>
-    <t>Seb Whipped Crème 150ml</t>
-  </si>
-  <si>
-    <t>Seb Re-Shaper (atomizador)</t>
-  </si>
-  <si>
-    <t>Seb Trilliant Thermal P. 150ml</t>
-  </si>
-  <si>
-    <t>Seb Potion 9 Styling Treat 150ml</t>
-  </si>
-  <si>
-    <t>Seb Potion 9 Styling Treat 500ml</t>
-  </si>
-  <si>
-    <t>Seb Thickefy Foam 200ml</t>
-  </si>
-  <si>
-    <t>SEBASTIAN DARK</t>
-  </si>
-  <si>
-    <t>SEBASTIAN</t>
-  </si>
-  <si>
     <t>ULTIMATE SMOOTH</t>
   </si>
   <si>
@@ -504,6 +378,129 @@
   </si>
   <si>
     <t>Neutralizante wallastrate x125ml</t>
+  </si>
+  <si>
+    <t>ULTIMATE COLOR</t>
+  </si>
+  <si>
+    <t>Wella Ultimate Color  SHP 1L MULTI</t>
+  </si>
+  <si>
+    <t>Wella Ultimate Color  CND 1L MULTI</t>
+  </si>
+  <si>
+    <t>Wella Ultimate Color  SEALER 185ml MULTI</t>
+  </si>
+  <si>
+    <t>Wella Ultimate Color  SPRAY 95ml EMEA</t>
+  </si>
+  <si>
+    <t>Wella Ultimate Color  SHP 250ml EMEA</t>
+  </si>
+  <si>
+    <t>Wella Ultimate Color  CND 200ml EMEA</t>
+  </si>
+  <si>
+    <t>Wella Ultimate Color  MASK 95ml EMEA</t>
+  </si>
+  <si>
+    <t>95 ml</t>
+  </si>
+  <si>
+    <t>NEW SEBASTIAN</t>
+  </si>
+  <si>
+    <t>SEB DARKOIL ATB SHAMP 1000ML AM BRZ</t>
+  </si>
+  <si>
+    <t>SEB DARKOIL ATB COND 1000ML AM BRZ</t>
+  </si>
+  <si>
+    <t>SEB DARKOIL ATB MASK 500ML AM BRZ</t>
+  </si>
+  <si>
+    <t>SEB DARKOIL OTC SHAMPOO 280ML AME BR</t>
+  </si>
+  <si>
+    <t>280 ml</t>
+  </si>
+  <si>
+    <t>SEB DARKOIL OTC COND 200ML AM BR</t>
+  </si>
+  <si>
+    <t>SEB DARKOIL OTC MASK 145ML AM BR</t>
+  </si>
+  <si>
+    <t>145 ml</t>
+  </si>
+  <si>
+    <t>SEB DARKOIL OTC HAIROIL 100ML AM</t>
+  </si>
+  <si>
+    <t>SEB DARKOIL MASK 30ML EMEA</t>
+  </si>
+  <si>
+    <t>SEB PENETRT ATB SHP 1000ML AM BR</t>
+  </si>
+  <si>
+    <t>SEB PENETRT ATB CND 1000ML AM BRZ</t>
+  </si>
+  <si>
+    <t>SEB PENET OTC SHAMPOO 280ML AMEBR</t>
+  </si>
+  <si>
+    <t>SEB PENETRT OTC CND 200ML AM BR</t>
+  </si>
+  <si>
+    <t>SEB PENETRT OTC MASK 145ML AM BR</t>
+  </si>
+  <si>
+    <t>SEB POTION9 SHP 1000ML AM BR</t>
+  </si>
+  <si>
+    <t>SEB POTION9 CND 1000ML AM BR</t>
+  </si>
+  <si>
+    <t>SEB POTION9 ATB CREAM 500ML AM BRZ</t>
+  </si>
+  <si>
+    <t>SEB POTION9 ATB ACT POWDER 15x2G ESPTGR</t>
+  </si>
+  <si>
+    <t>15 x 2 g</t>
+  </si>
+  <si>
+    <t>SEB POTION9 OTC SHAMPOO 280ML AMEBR</t>
+  </si>
+  <si>
+    <t>SEB POTION9 OTC COND 200ML AM BR</t>
+  </si>
+  <si>
+    <t>SEB POTION9 OTC CREAM 145ML AM BRZ</t>
+  </si>
+  <si>
+    <t>SEB POTION9 OTC DROPS 30ML AM BR</t>
+  </si>
+  <si>
+    <t>SEB POTION9 SHAMP 50ML AM BR</t>
+  </si>
+  <si>
+    <t>50 ml</t>
+  </si>
+  <si>
+    <t>SEB SHAPR OTC H/S 300ML ENESPTARTR</t>
+  </si>
+  <si>
+    <t>300 ml</t>
+  </si>
+  <si>
+    <t>SEB FORM OTC 150 ML SPRAY TR/MEX/E</t>
+  </si>
+  <si>
+    <t>SEB OTH OTC THICKEFY FOAM 190ML IV</t>
+  </si>
+  <si>
+    <t>190 ml</t>
   </si>
 </sst>
 </file>
@@ -781,10 +778,6 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
@@ -815,6 +808,10 @@
     <xf numFmtId="4" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -822,7 +819,107 @@
     <cellStyle name="Normal 6 2" xfId="3"/>
     <cellStyle name="Normal_Wella precios Oct 2009- lista 27" xfId="1"/>
   </cellStyles>
-  <dxfs count="67">
+  <dxfs count="87">
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color theme="0" tint="-0.24994659260841701"/>
@@ -1434,7 +1531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F131"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" customWidth="1"/>
@@ -1460,197 +1557,197 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="18" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="24"/>
+        <v>101</v>
+      </c>
+      <c r="C2" s="20"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="23"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="5" t="s">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="E3" s="6"/>
-      <c r="F3" s="20"/>
+      <c r="F3" s="19"/>
     </row>
     <row r="4" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="5" t="s">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="E4" s="6"/>
-      <c r="F4" s="20"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>147</v>
+        <v>105</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="5" t="s">
-        <v>141</v>
+        <v>99</v>
       </c>
       <c r="E5" s="6"/>
-      <c r="F5" s="20"/>
+      <c r="F5" s="19"/>
     </row>
     <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="6"/>
-      <c r="F6" s="20"/>
+      <c r="F6" s="19"/>
     </row>
     <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="6"/>
-      <c r="F7" s="20"/>
+      <c r="F7" s="19"/>
     </row>
     <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>151</v>
+        <v>109</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="6"/>
-      <c r="F8" s="20"/>
+      <c r="F8" s="19"/>
     </row>
     <row r="9" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="6"/>
-      <c r="F9" s="20"/>
+      <c r="F9" s="19"/>
     </row>
     <row r="10" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>153</v>
+        <v>111</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="6"/>
-      <c r="F10" s="20"/>
+      <c r="F10" s="19"/>
     </row>
     <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="6"/>
-      <c r="F11" s="20"/>
+      <c r="F11" s="19"/>
     </row>
     <row r="12" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>155</v>
+        <v>113</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="6"/>
-      <c r="F12" s="20"/>
+      <c r="F12" s="19"/>
     </row>
     <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="5"/>
       <c r="E13" s="6"/>
-      <c r="F13" s="20"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="5"/>
       <c r="E14" s="6"/>
-      <c r="F14" s="20"/>
+      <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="5"/>
       <c r="E15" s="6"/>
-      <c r="F15" s="20"/>
+      <c r="F15" s="19"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -1668,7 +1765,7 @@
       <c r="E16" s="6">
         <v>113135</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="19">
         <v>42425.625</v>
       </c>
     </row>
@@ -1688,7 +1785,7 @@
       <c r="E17" s="6">
         <v>138424</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="19">
         <v>51909</v>
       </c>
     </row>
@@ -1708,7 +1805,7 @@
       <c r="E18" s="6">
         <v>106480</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="19">
         <v>39930</v>
       </c>
     </row>
@@ -1728,7 +1825,7 @@
       <c r="E19" s="6">
         <v>43923</v>
       </c>
-      <c r="F19" s="20">
+      <c r="F19" s="19">
         <v>21961.5</v>
       </c>
     </row>
@@ -1748,7 +1845,7 @@
       <c r="E20" s="6">
         <v>48581.5</v>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="19">
         <v>24290.75</v>
       </c>
     </row>
@@ -1768,7 +1865,7 @@
       <c r="E21" s="6">
         <v>60560.5</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="19">
         <v>30280.25</v>
       </c>
     </row>
@@ -1788,7 +1885,7 @@
       <c r="E22" s="6">
         <v>60161.2</v>
       </c>
-      <c r="F22" s="20">
+      <c r="F22" s="19">
         <v>30080.6</v>
       </c>
     </row>
@@ -1808,7 +1905,7 @@
       <c r="E23" s="11">
         <v>113135</v>
       </c>
-      <c r="F23" s="20">
+      <c r="F23" s="19">
         <v>42425.625</v>
       </c>
     </row>
@@ -1828,7 +1925,7 @@
       <c r="E24" s="11">
         <v>118325.9</v>
       </c>
-      <c r="F24" s="20">
+      <c r="F24" s="19">
         <v>44372.212499999994</v>
       </c>
     </row>
@@ -1848,7 +1945,7 @@
       <c r="E25" s="11">
         <v>138424</v>
       </c>
-      <c r="F25" s="20">
+      <c r="F25" s="19">
         <v>51909</v>
       </c>
     </row>
@@ -1868,7 +1965,7 @@
       <c r="E26" s="11">
         <v>61226</v>
       </c>
-      <c r="F26" s="20">
+      <c r="F26" s="19">
         <v>22959.75</v>
       </c>
     </row>
@@ -1888,7 +1985,7 @@
       <c r="E27" s="11">
         <v>43923</v>
       </c>
-      <c r="F27" s="20">
+      <c r="F27" s="19">
         <v>21961.5</v>
       </c>
     </row>
@@ -1908,7 +2005,7 @@
       <c r="E28" s="11">
         <v>48581.5</v>
       </c>
-      <c r="F28" s="20">
+      <c r="F28" s="19">
         <v>24290.75</v>
       </c>
     </row>
@@ -1928,7 +2025,7 @@
       <c r="E29" s="11">
         <v>60560.5</v>
       </c>
-      <c r="F29" s="20">
+      <c r="F29" s="19">
         <v>30280.25</v>
       </c>
     </row>
@@ -1948,7 +2045,7 @@
       <c r="E30" s="12">
         <v>113135</v>
       </c>
-      <c r="F30" s="20">
+      <c r="F30" s="19">
         <v>42425.625</v>
       </c>
     </row>
@@ -1968,7 +2065,7 @@
       <c r="E31" s="12">
         <v>138424</v>
       </c>
-      <c r="F31" s="20">
+      <c r="F31" s="19">
         <v>51909</v>
       </c>
     </row>
@@ -1988,7 +2085,7 @@
       <c r="E32" s="12">
         <v>149072</v>
       </c>
-      <c r="F32" s="20">
+      <c r="F32" s="19">
         <v>55902</v>
       </c>
     </row>
@@ -2008,7 +2105,7 @@
       <c r="E33" s="12">
         <v>61492.2</v>
       </c>
-      <c r="F33" s="20">
+      <c r="F33" s="19">
         <v>23059.574999999997</v>
       </c>
     </row>
@@ -2028,7 +2125,7 @@
       <c r="E34" s="12">
         <v>43923</v>
       </c>
-      <c r="F34" s="20">
+      <c r="F34" s="19">
         <v>21961.5</v>
       </c>
     </row>
@@ -2048,7 +2145,7 @@
       <c r="E35" s="12">
         <v>48581.5</v>
       </c>
-      <c r="F35" s="20">
+      <c r="F35" s="19">
         <v>24290.75</v>
       </c>
     </row>
@@ -2068,13 +2165,13 @@
       <c r="E36" s="12">
         <v>60560.5</v>
       </c>
-      <c r="F36" s="20">
+      <c r="F36" s="19">
         <v>30280.25</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>140</v>
+        <v>98</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>44</v>
@@ -2088,13 +2185,13 @@
       <c r="E37" s="13">
         <v>113135</v>
       </c>
-      <c r="F37" s="20">
+      <c r="F37" s="19">
         <v>42425.625</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>98</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>45</v>
@@ -2108,13 +2205,13 @@
       <c r="E38" s="13">
         <v>118325.9</v>
       </c>
-      <c r="F38" s="20">
+      <c r="F38" s="19">
         <v>44372.212499999994</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>140</v>
+        <v>98</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>46</v>
@@ -2128,13 +2225,13 @@
       <c r="E39" s="13">
         <v>118325.9</v>
       </c>
-      <c r="F39" s="20">
+      <c r="F39" s="19">
         <v>44372.212499999994</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>140</v>
+        <v>98</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>47</v>
@@ -2148,13 +2245,13 @@
       <c r="E40" s="13">
         <v>149072</v>
       </c>
-      <c r="F40" s="20">
+      <c r="F40" s="19">
         <v>55902</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>140</v>
+        <v>98</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>48</v>
@@ -2168,13 +2265,13 @@
       <c r="E41" s="13">
         <v>43923</v>
       </c>
-      <c r="F41" s="20">
+      <c r="F41" s="19">
         <v>21961.5</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>140</v>
+        <v>98</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>49</v>
@@ -2188,13 +2285,13 @@
       <c r="E42" s="13">
         <v>48581.5</v>
       </c>
-      <c r="F42" s="20">
+      <c r="F42" s="19">
         <v>24290.75</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>140</v>
+        <v>98</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>50</v>
@@ -2208,13 +2305,13 @@
       <c r="E43" s="13">
         <v>48581.5</v>
       </c>
-      <c r="F43" s="20">
+      <c r="F43" s="19">
         <v>24290.75</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>140</v>
+        <v>98</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>51</v>
@@ -2228,13 +2325,13 @@
       <c r="E44" s="13">
         <v>60560.5</v>
       </c>
-      <c r="F44" s="20">
+      <c r="F44" s="19">
         <v>30280.25</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>140</v>
+        <v>98</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>52</v>
@@ -2248,7 +2345,7 @@
       <c r="E45" s="13">
         <v>60560.5</v>
       </c>
-      <c r="F45" s="20">
+      <c r="F45" s="19">
         <v>30280.25</v>
       </c>
     </row>
@@ -2268,7 +2365,7 @@
       <c r="E46" s="12">
         <v>97163</v>
       </c>
-      <c r="F46" s="20">
+      <c r="F46" s="19">
         <v>36436.125</v>
       </c>
     </row>
@@ -2288,7 +2385,7 @@
       <c r="E47" s="12">
         <v>99825</v>
       </c>
-      <c r="F47" s="20">
+      <c r="F47" s="19">
         <v>37434.375</v>
       </c>
     </row>
@@ -2308,7 +2405,7 @@
       <c r="E48" s="12">
         <v>119124.5</v>
       </c>
-      <c r="F48" s="20">
+      <c r="F48" s="19">
         <v>44671.6875</v>
       </c>
     </row>
@@ -2328,7 +2425,7 @@
       <c r="E49" s="12">
         <v>59495.7</v>
       </c>
-      <c r="F49" s="20">
+      <c r="F49" s="19">
         <v>22310.887499999997</v>
       </c>
     </row>
@@ -2348,7 +2445,7 @@
       <c r="E50" s="12">
         <v>35937</v>
       </c>
-      <c r="F50" s="20">
+      <c r="F50" s="19">
         <v>17968.5</v>
       </c>
     </row>
@@ -2368,7 +2465,7 @@
       <c r="E51" s="12">
         <v>41261</v>
       </c>
-      <c r="F51" s="20">
+      <c r="F51" s="19">
         <v>20630.5</v>
       </c>
     </row>
@@ -2388,7 +2485,7 @@
       <c r="E52" s="12">
         <v>51909</v>
       </c>
-      <c r="F52" s="20">
+      <c r="F52" s="19">
         <v>25954.5</v>
       </c>
     </row>
@@ -2408,7 +2505,7 @@
       <c r="E53" s="12">
         <v>97163</v>
       </c>
-      <c r="F53" s="20">
+      <c r="F53" s="19">
         <v>36436.125</v>
       </c>
     </row>
@@ -2428,7 +2525,7 @@
       <c r="E54" s="12">
         <v>99825</v>
       </c>
-      <c r="F54" s="20">
+      <c r="F54" s="19">
         <v>37434.375</v>
       </c>
     </row>
@@ -2448,7 +2545,7 @@
       <c r="E55" s="12">
         <v>119124.5</v>
       </c>
-      <c r="F55" s="20">
+      <c r="F55" s="19">
         <v>44671.6875</v>
       </c>
     </row>
@@ -2468,7 +2565,7 @@
       <c r="E56" s="12">
         <v>59495.7</v>
       </c>
-      <c r="F56" s="20">
+      <c r="F56" s="19">
         <v>22310.887499999997</v>
       </c>
     </row>
@@ -2488,7 +2585,7 @@
       <c r="E57" s="12">
         <v>35937</v>
       </c>
-      <c r="F57" s="20">
+      <c r="F57" s="19">
         <v>17968.5</v>
       </c>
     </row>
@@ -2508,7 +2605,7 @@
       <c r="E58" s="12">
         <v>41261</v>
       </c>
-      <c r="F58" s="20">
+      <c r="F58" s="19">
         <v>20630.5</v>
       </c>
     </row>
@@ -2528,7 +2625,7 @@
       <c r="E59" s="12">
         <v>51909</v>
       </c>
-      <c r="F59" s="20">
+      <c r="F59" s="19">
         <v>25954.5</v>
       </c>
     </row>
@@ -2548,7 +2645,7 @@
       <c r="E60" s="12">
         <v>51909</v>
       </c>
-      <c r="F60" s="20">
+      <c r="F60" s="19">
         <v>25954.5</v>
       </c>
     </row>
@@ -2568,7 +2665,7 @@
       <c r="E61" s="12">
         <v>97163</v>
       </c>
-      <c r="F61" s="20">
+      <c r="F61" s="19">
         <v>36436.125</v>
       </c>
     </row>
@@ -2588,7 +2685,7 @@
       <c r="E62" s="12">
         <v>35937</v>
       </c>
-      <c r="F62" s="20">
+      <c r="F62" s="19">
         <v>17968.5</v>
       </c>
     </row>
@@ -2608,7 +2705,7 @@
       <c r="E63" s="12">
         <v>41261</v>
       </c>
-      <c r="F63" s="20">
+      <c r="F63" s="19">
         <v>20630.5</v>
       </c>
     </row>
@@ -2628,7 +2725,7 @@
       <c r="E64" s="12">
         <v>97163</v>
       </c>
-      <c r="F64" s="20">
+      <c r="F64" s="19">
         <v>36436.125</v>
       </c>
     </row>
@@ -2648,7 +2745,7 @@
       <c r="E65" s="12">
         <v>35937</v>
       </c>
-      <c r="F65" s="20">
+      <c r="F65" s="19">
         <v>17968.5</v>
       </c>
     </row>
@@ -2668,7 +2765,7 @@
       <c r="E66" s="11">
         <v>137026.44999999998</v>
       </c>
-      <c r="F66" s="20">
+      <c r="F66" s="19">
         <v>51384.918749999997</v>
       </c>
     </row>
@@ -2688,7 +2785,7 @@
       <c r="E67" s="11">
         <v>143282.15</v>
       </c>
-      <c r="F67" s="20">
+      <c r="F67" s="19">
         <v>53730.806249999994</v>
       </c>
     </row>
@@ -2708,7 +2805,7 @@
       <c r="E68" s="11">
         <v>143282.15</v>
       </c>
-      <c r="F68" s="20">
+      <c r="F68" s="19">
         <v>53730.806249999994</v>
       </c>
     </row>
@@ -2717,18 +2814,18 @@
         <v>74</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>138</v>
+        <v>96</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>139</v>
+        <v>97</v>
       </c>
       <c r="E69" s="11">
         <v>181500</v>
       </c>
-      <c r="F69" s="20">
+      <c r="F69" s="19">
         <v>68062.5</v>
       </c>
     </row>
@@ -2748,7 +2845,7 @@
       <c r="E70" s="11">
         <v>47183.95</v>
       </c>
-      <c r="F70" s="20">
+      <c r="F70" s="19">
         <v>23591.974999999999</v>
       </c>
     </row>
@@ -2768,7 +2865,7 @@
       <c r="E71" s="11">
         <v>51376.6</v>
       </c>
-      <c r="F71" s="20">
+      <c r="F71" s="19">
         <v>25688.3</v>
       </c>
     </row>
@@ -2788,7 +2885,7 @@
       <c r="E72" s="11">
         <v>67747.899999999994</v>
       </c>
-      <c r="F72" s="20">
+      <c r="F72" s="19">
         <v>33873.949999999997</v>
       </c>
     </row>
@@ -2808,7 +2905,7 @@
       <c r="E73" s="11">
         <v>55768.9</v>
       </c>
-      <c r="F73" s="20">
+      <c r="F73" s="19">
         <v>27884.450000000004</v>
       </c>
     </row>
@@ -2828,7 +2925,7 @@
       <c r="E74" s="11">
         <v>67747.899999999994</v>
       </c>
-      <c r="F74" s="20">
+      <c r="F74" s="19">
         <v>33873.949999999997</v>
       </c>
     </row>
@@ -2837,7 +2934,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>30</v>
@@ -2848,16 +2945,16 @@
       <c r="E75" s="11">
         <v>55768.9</v>
       </c>
-      <c r="F75" s="20">
+      <c r="F75" s="19">
         <v>27884.450000000004</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>7</v>
@@ -2868,16 +2965,16 @@
       <c r="E76" s="11">
         <v>137026.44999999998</v>
       </c>
-      <c r="F76" s="20">
+      <c r="F76" s="19">
         <v>51384.918749999997</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>18</v>
@@ -2888,16 +2985,16 @@
       <c r="E77" s="11">
         <v>143282.15</v>
       </c>
-      <c r="F77" s="20">
+      <c r="F77" s="19">
         <v>53730.806249999994</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>10</v>
@@ -2908,16 +3005,16 @@
       <c r="E78" s="11">
         <v>143282.15</v>
       </c>
-      <c r="F78" s="20">
+      <c r="F78" s="19">
         <v>53730.806249999994</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>30</v>
@@ -2928,16 +3025,16 @@
       <c r="E79" s="11">
         <v>143282.15</v>
       </c>
-      <c r="F79" s="20">
+      <c r="F79" s="19">
         <v>53730.806249999994</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>7</v>
@@ -2948,16 +3045,16 @@
       <c r="E80" s="11">
         <v>47183.95</v>
       </c>
-      <c r="F80" s="20">
+      <c r="F80" s="19">
         <v>31613.246500000001</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>134</v>
+        <v>92</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>18</v>
@@ -2968,16 +3065,16 @@
       <c r="E81" s="11">
         <v>51376.6</v>
       </c>
-      <c r="F81" s="20">
+      <c r="F81" s="19">
         <v>34422.322</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>135</v>
+        <v>93</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>10</v>
@@ -2988,16 +3085,16 @@
       <c r="E82" s="11">
         <v>67747.899999999994</v>
       </c>
-      <c r="F82" s="20">
+      <c r="F82" s="19">
         <v>45391.092999999993</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>30</v>
@@ -3008,950 +3105,957 @@
       <c r="E83" s="11">
         <v>55768.9</v>
       </c>
-      <c r="F83" s="20">
+      <c r="F83" s="19">
         <v>37365.163</v>
       </c>
     </row>
     <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="17"/>
-      <c r="B84" s="17"/>
-      <c r="C84" s="17"/>
-      <c r="D84" s="17"/>
-      <c r="E84" s="18"/>
-      <c r="F84" s="20"/>
+      <c r="A84" s="16"/>
+      <c r="B84" s="16"/>
+      <c r="C84" s="16"/>
+      <c r="D84" s="16"/>
+      <c r="E84" s="17"/>
+      <c r="F84" s="19"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B85" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C85" s="15"/>
-      <c r="D85" s="10"/>
-      <c r="E85" s="16">
-        <v>69212</v>
-      </c>
-      <c r="F85" s="20">
-        <v>34606</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E85" s="17"/>
+      <c r="F85" s="19"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B86" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C86" s="15"/>
-      <c r="D86" s="10"/>
-      <c r="E86" s="16">
-        <v>172364.5</v>
-      </c>
-      <c r="F86" s="20">
-        <v>64636.6875</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E86" s="17"/>
+      <c r="F86" s="19"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B87" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="C87" s="15"/>
-      <c r="D87" s="10"/>
-      <c r="E87" s="16">
-        <v>181681.5</v>
-      </c>
-      <c r="F87" s="20">
-        <v>68130.5625</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D87" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="E87" s="17"/>
+      <c r="F87" s="19"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D88" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="B88" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="C88" s="15"/>
-      <c r="D88" s="10"/>
-      <c r="E88" s="16">
-        <v>179685</v>
-      </c>
-      <c r="F88" s="20">
-        <v>67381.875</v>
-      </c>
+      <c r="E88" s="17"/>
+      <c r="F88" s="19"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B89" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="C89" s="15"/>
-      <c r="D89" s="10"/>
-      <c r="E89" s="16">
-        <v>58297.799999999996</v>
-      </c>
-      <c r="F89" s="20">
-        <v>29148.899999999998</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E89" s="17"/>
+      <c r="F89" s="19"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B90" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="C90" s="15"/>
-      <c r="D90" s="10"/>
-      <c r="E90" s="16">
-        <v>66283.8</v>
-      </c>
-      <c r="F90" s="20">
-        <v>33141.900000000009</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D90" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E90" s="17"/>
+      <c r="F90" s="19"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="B91" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="C91" s="15"/>
-      <c r="D91" s="10"/>
-      <c r="E91" s="16">
-        <v>77198</v>
-      </c>
-      <c r="F91" s="20">
-        <v>38599</v>
-      </c>
+      <c r="E91" s="17"/>
+      <c r="F91" s="19"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="4" t="s">
+      <c r="A92" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B92" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="C92" s="15"/>
-      <c r="D92" s="10"/>
-      <c r="E92" s="16">
-        <v>145079</v>
-      </c>
-      <c r="F92" s="20">
-        <v>54404.625</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="C92" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D92" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E92" s="15"/>
+      <c r="F92" s="19"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="4" t="s">
+      <c r="A93" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B93" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="C93" s="15"/>
-      <c r="D93" s="10"/>
-      <c r="E93" s="16">
-        <v>151734</v>
-      </c>
-      <c r="F93" s="20">
-        <v>56900.25</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="C93" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D93" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E93" s="15"/>
+      <c r="F93" s="19"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="4" t="s">
+      <c r="A94" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B94" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="C94" s="10"/>
-      <c r="D94" s="10"/>
-      <c r="E94" s="16">
-        <v>151734</v>
-      </c>
-      <c r="F94" s="20">
-        <v>56900.25</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="C94" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D94" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E94" s="15"/>
+      <c r="F94" s="19"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="4" t="s">
+      <c r="A95" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B95" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="C95" s="15"/>
-      <c r="D95" s="10"/>
-      <c r="E95" s="16">
-        <v>49247</v>
-      </c>
-      <c r="F95" s="20">
-        <v>24623.5</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="C95" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D95" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E95" s="15"/>
+      <c r="F95" s="19"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="4" t="s">
+      <c r="A96" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B96" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="C96" s="15"/>
-      <c r="D96" s="10"/>
-      <c r="E96" s="16">
-        <v>55902</v>
-      </c>
-      <c r="F96" s="20">
-        <v>27951</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="C96" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D96" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E96" s="15"/>
+      <c r="F96" s="19"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="4" t="s">
+      <c r="A97" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B97" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="C97" s="10"/>
-      <c r="D97" s="10"/>
-      <c r="E97" s="16">
-        <v>65219</v>
-      </c>
-      <c r="F97" s="20">
-        <v>32609.5</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="C97" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D97" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="E97" s="15"/>
+      <c r="F97" s="19"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="4" t="s">
+      <c r="A98" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B98" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="C98" s="15"/>
-      <c r="D98" s="10"/>
-      <c r="E98" s="16">
-        <v>145079</v>
-      </c>
-      <c r="F98" s="20">
-        <v>54404.625</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="C98" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D98" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E98" s="15"/>
+      <c r="F98" s="19"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="4" t="s">
+      <c r="A99" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B99" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="C99" s="15"/>
-      <c r="D99" s="10"/>
-      <c r="E99" s="16">
-        <v>151734</v>
-      </c>
-      <c r="F99" s="20">
-        <v>56900.25</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="C99" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D99" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E99" s="15"/>
+      <c r="F99" s="19"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="4" t="s">
+      <c r="A100" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B100" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="C100" s="10"/>
-      <c r="D100" s="10"/>
-      <c r="E100" s="16">
-        <v>151734</v>
-      </c>
-      <c r="F100" s="20">
-        <v>56900.25</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="C100" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D100" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="15"/>
+      <c r="F100" s="19"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" s="4" t="s">
+      <c r="A101" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B101" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="C101" s="15"/>
-      <c r="D101" s="10"/>
-      <c r="E101" s="16">
-        <v>55902</v>
-      </c>
-      <c r="F101" s="20">
-        <v>27951</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="C101" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D101" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="15"/>
+      <c r="F101" s="19"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" s="4" t="s">
+      <c r="A102" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B102" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C102" s="15"/>
-      <c r="D102" s="10"/>
-      <c r="E102" s="16">
-        <v>55902</v>
-      </c>
-      <c r="F102" s="20">
-        <v>27951</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="C102" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D102" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E102" s="15"/>
+      <c r="F102" s="19"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="4" t="s">
+      <c r="A103" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B103" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="C103" s="10"/>
-      <c r="D103" s="10"/>
-      <c r="E103" s="16">
-        <v>65219</v>
-      </c>
-      <c r="F103" s="20">
-        <v>32609.5</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C103" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D103" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E103" s="15"/>
+      <c r="F103" s="19"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="4" t="s">
+      <c r="A104" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B104" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="C104" s="10"/>
-      <c r="D104" s="10"/>
-      <c r="E104" s="16">
-        <v>145079</v>
-      </c>
-      <c r="F104" s="20">
-        <v>54404.625</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="C104" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D104" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="E104" s="15"/>
+      <c r="F104" s="19"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="4" t="s">
+      <c r="A105" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B105" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="C105" s="10"/>
-      <c r="D105" s="10"/>
-      <c r="E105" s="16">
-        <v>151734</v>
-      </c>
-      <c r="F105" s="20">
-        <v>56900.25</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="C105" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D105" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E105" s="15"/>
+      <c r="F105" s="19"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="4" t="s">
+      <c r="A106" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B106" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="C106" s="10"/>
-      <c r="D106" s="10"/>
-      <c r="E106" s="16">
-        <v>55902</v>
-      </c>
-      <c r="F106" s="20">
-        <v>27951</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="C106" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D106" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E106" s="15"/>
+      <c r="F106" s="19"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="4" t="s">
+      <c r="A107" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B107" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C107" s="10"/>
-      <c r="D107" s="10"/>
-      <c r="E107" s="16">
-        <v>55902</v>
-      </c>
-      <c r="F107" s="20">
-        <v>27951</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="C107" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D107" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E107" s="15"/>
+      <c r="F107" s="19"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108" s="4" t="s">
+      <c r="A108" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B108" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="C108" s="10"/>
-      <c r="D108" s="10"/>
-      <c r="E108" s="16">
-        <v>145478.29999999999</v>
-      </c>
-      <c r="F108" s="20">
-        <v>54554.362499999996</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C108" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D108" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="E108" s="15"/>
+      <c r="F108" s="19"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109" s="4" t="s">
+      <c r="A109" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B109" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="C109" s="10"/>
-      <c r="D109" s="10"/>
-      <c r="E109" s="16">
-        <v>151734</v>
-      </c>
-      <c r="F109" s="20">
-        <v>56900.25</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="C109" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D109" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E109" s="15"/>
+      <c r="F109" s="19"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110" s="4" t="s">
+      <c r="A110" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B110" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="C110" s="10"/>
-      <c r="D110" s="10"/>
-      <c r="E110" s="16">
-        <v>55902</v>
-      </c>
-      <c r="F110" s="20">
-        <v>27951</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="C110" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D110" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E110" s="15"/>
+      <c r="F110" s="19"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111" s="4" t="s">
+      <c r="A111" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B111" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="C111" s="10"/>
-      <c r="D111" s="10"/>
-      <c r="E111" s="16">
-        <v>55902</v>
-      </c>
-      <c r="F111" s="20">
-        <v>27951</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="C111" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D111" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="E111" s="15"/>
+      <c r="F111" s="19"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="4" t="s">
+      <c r="A112" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B112" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="C112" s="10"/>
-      <c r="D112" s="10"/>
-      <c r="E112" s="16">
-        <v>65219</v>
-      </c>
-      <c r="F112" s="20">
-        <v>32609.5</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="C112" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D112" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E112" s="15"/>
+      <c r="F112" s="19"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="4" t="s">
+      <c r="A113" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B113" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="C113" s="10"/>
-      <c r="D113" s="10"/>
-      <c r="E113" s="16">
-        <v>65219</v>
-      </c>
-      <c r="F113" s="20">
-        <v>32609.5</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="C113" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D113" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="E113" s="15"/>
+      <c r="F113" s="19"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="4" t="s">
+      <c r="A114" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B114" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="C114" s="10"/>
-      <c r="D114" s="10"/>
-      <c r="E114" s="16">
-        <v>55902</v>
-      </c>
-      <c r="F114" s="20">
-        <v>27951</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="C114" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D114" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="E114" s="15"/>
+      <c r="F114" s="19"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" s="4" t="s">
+      <c r="A115" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B115" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C115" s="10"/>
-      <c r="D115" s="10"/>
-      <c r="E115" s="16">
-        <v>44588.5</v>
-      </c>
-      <c r="F115" s="20">
-        <v>22294.25</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="C115" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D115" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E115" s="15"/>
+      <c r="F115" s="19"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" s="4" t="s">
+      <c r="A116" s="24" t="s">
         <v>127</v>
       </c>
       <c r="B116" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C116" s="10"/>
-      <c r="D116" s="10"/>
-      <c r="E116" s="16">
-        <v>44588.5</v>
-      </c>
-      <c r="F116" s="20">
-        <v>22294.25</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="C116" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D116" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="E116" s="15"/>
+      <c r="F116" s="19"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B117" s="14" t="s">
-        <v>118</v>
-      </c>
+      <c r="A117" s="4"/>
+      <c r="B117" s="14"/>
       <c r="C117" s="10"/>
       <c r="D117" s="10"/>
-      <c r="E117" s="16">
-        <v>48581.5</v>
-      </c>
-      <c r="F117" s="20">
-        <v>24290.75</v>
-      </c>
+      <c r="E117" s="15"/>
+      <c r="F117" s="19"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B118" s="14" t="s">
-        <v>119</v>
-      </c>
+      <c r="A118" s="4"/>
+      <c r="B118" s="14"/>
       <c r="C118" s="10"/>
       <c r="D118" s="10"/>
-      <c r="E118" s="16">
-        <v>48581.5</v>
-      </c>
-      <c r="F118" s="20">
-        <v>24290.75</v>
-      </c>
+      <c r="E118" s="15"/>
+      <c r="F118" s="19"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B119" s="14" t="s">
-        <v>120</v>
-      </c>
+      <c r="A119" s="4"/>
+      <c r="B119" s="14"/>
       <c r="C119" s="10"/>
       <c r="D119" s="10"/>
-      <c r="E119" s="16">
-        <v>63222.5</v>
-      </c>
-      <c r="F119" s="20">
-        <v>31611.25</v>
-      </c>
+      <c r="E119" s="15"/>
+      <c r="F119" s="19"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A120" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B120" s="14" t="s">
-        <v>121</v>
-      </c>
+      <c r="A120" s="4"/>
+      <c r="B120" s="14"/>
       <c r="C120" s="10"/>
       <c r="D120" s="10"/>
-      <c r="E120" s="16">
-        <v>56567.5</v>
-      </c>
-      <c r="F120" s="20">
-        <v>28283.75</v>
-      </c>
+      <c r="E120" s="15"/>
+      <c r="F120" s="19"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B121" s="14" t="s">
-        <v>122</v>
-      </c>
+      <c r="A121" s="4"/>
+      <c r="B121" s="14"/>
       <c r="C121" s="10"/>
       <c r="D121" s="10"/>
-      <c r="E121" s="16">
-        <v>48581.5</v>
-      </c>
-      <c r="F121" s="20">
-        <v>24290.75</v>
-      </c>
+      <c r="E121" s="15"/>
+      <c r="F121" s="19"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B122" s="14" t="s">
-        <v>123</v>
-      </c>
+      <c r="A122" s="4"/>
+      <c r="B122" s="14"/>
       <c r="C122" s="10"/>
       <c r="D122" s="10"/>
-      <c r="E122" s="16">
-        <v>69877.5</v>
-      </c>
-      <c r="F122" s="20">
-        <v>34938.75</v>
-      </c>
+      <c r="E122" s="15"/>
+      <c r="F122" s="19"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B123" s="14" t="s">
-        <v>124</v>
-      </c>
+      <c r="A123" s="4"/>
+      <c r="B123" s="14"/>
       <c r="C123" s="10"/>
       <c r="D123" s="10"/>
-      <c r="E123" s="16">
-        <v>140686.69999999998</v>
-      </c>
-      <c r="F123" s="20">
-        <v>52757.512499999997</v>
-      </c>
+      <c r="E123" s="15"/>
+      <c r="F123" s="19"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B124" s="14" t="s">
-        <v>125</v>
-      </c>
+      <c r="A124" s="4"/>
+      <c r="B124" s="14"/>
       <c r="C124" s="10"/>
       <c r="D124" s="10"/>
-      <c r="E124" s="16">
-        <v>52574.5</v>
-      </c>
-      <c r="F124" s="20">
-        <v>26287.25</v>
-      </c>
+      <c r="E124" s="15"/>
+      <c r="F124" s="19"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="4"/>
+      <c r="B125" s="14"/>
+      <c r="C125" s="10"/>
+      <c r="D125" s="10"/>
+      <c r="E125" s="15"/>
+      <c r="F125" s="19"/>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="4"/>
+      <c r="B126" s="14"/>
+      <c r="C126" s="10"/>
+      <c r="D126" s="10"/>
+      <c r="E126" s="15"/>
+      <c r="F126" s="19"/>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="4"/>
+      <c r="B127" s="14"/>
+      <c r="C127" s="10"/>
+      <c r="D127" s="10"/>
+      <c r="E127" s="15"/>
+      <c r="F127" s="19"/>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="4"/>
+      <c r="B128" s="14"/>
+      <c r="C128" s="10"/>
+      <c r="D128" s="10"/>
+      <c r="E128" s="15"/>
+      <c r="F128" s="19"/>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="4"/>
+      <c r="B129" s="14"/>
+      <c r="C129" s="10"/>
+      <c r="D129" s="10"/>
+      <c r="E129" s="15"/>
+      <c r="F129" s="19"/>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" s="4"/>
+      <c r="B130" s="14"/>
+      <c r="C130" s="10"/>
+      <c r="D130" s="10"/>
+      <c r="E130" s="15"/>
+      <c r="F130" s="19"/>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" s="4"/>
+      <c r="B131" s="14"/>
+      <c r="C131" s="10"/>
+      <c r="D131" s="10"/>
+      <c r="E131" s="15"/>
+      <c r="F131" s="19"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A19:A23 C54:D55 B57 A46:A65 C57:D59">
-    <cfRule type="expression" dxfId="66" priority="49">
+    <cfRule type="expression" dxfId="86" priority="63">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:D18 A30:A45">
-    <cfRule type="expression" dxfId="65" priority="50">
+    <cfRule type="expression" dxfId="85" priority="64">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C61:D61 C63:D64 D62">
-    <cfRule type="expression" dxfId="64" priority="69">
+    <cfRule type="expression" dxfId="84" priority="83">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:B22 B17:D17 A16:A17 C19:D22">
-    <cfRule type="expression" dxfId="63" priority="68">
+    <cfRule type="expression" dxfId="83" priority="82">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16 D16 B19:B20">
-    <cfRule type="expression" dxfId="62" priority="67">
+    <cfRule type="expression" dxfId="82" priority="81">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16">
-    <cfRule type="expression" dxfId="61" priority="66">
+    <cfRule type="expression" dxfId="81" priority="80">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16">
-    <cfRule type="expression" dxfId="60" priority="65">
+    <cfRule type="expression" dxfId="80" priority="79">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24:B25 B28:B29 C24:D29 A23:A29">
-    <cfRule type="expression" dxfId="59" priority="64">
+    <cfRule type="expression" dxfId="79" priority="78">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23 D23 B26">
-    <cfRule type="expression" dxfId="58" priority="63">
+    <cfRule type="expression" dxfId="78" priority="77">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C23">
-    <cfRule type="expression" dxfId="57" priority="62">
+    <cfRule type="expression" dxfId="77" priority="76">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47:B48 B54:B55 B61:B62 B51:B52 B58:B59 C47:D52">
-    <cfRule type="expression" dxfId="56" priority="61">
+    <cfRule type="expression" dxfId="76" priority="75">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46 B53 B60 D46 D53 D60 B49:B50 B63:B64">
-    <cfRule type="expression" dxfId="55" priority="60">
+    <cfRule type="expression" dxfId="75" priority="74">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C46 C53 C60">
-    <cfRule type="expression" dxfId="54" priority="59">
+    <cfRule type="expression" dxfId="74" priority="73">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:B32 B35:B36 C31:D36 A30:A36">
-    <cfRule type="expression" dxfId="53" priority="58">
+    <cfRule type="expression" dxfId="73" priority="72">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30 D30 B33:B34">
-    <cfRule type="expression" dxfId="52" priority="57">
+    <cfRule type="expression" dxfId="72" priority="71">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30">
-    <cfRule type="expression" dxfId="51" priority="56">
+    <cfRule type="expression" dxfId="71" priority="70">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C62">
-    <cfRule type="expression" dxfId="50" priority="55">
+    <cfRule type="expression" dxfId="70" priority="69">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65">
-    <cfRule type="expression" dxfId="49" priority="53">
+    <cfRule type="expression" dxfId="69" priority="67">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C65:D65">
-    <cfRule type="expression" dxfId="48" priority="54">
+    <cfRule type="expression" dxfId="68" priority="68">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37:B38 B40:B41 B43:B44 C37:D45 A37:A45">
-    <cfRule type="expression" dxfId="47" priority="52">
+    <cfRule type="expression" dxfId="67" priority="66">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B39 B42 B45">
-    <cfRule type="expression" dxfId="46" priority="51">
+    <cfRule type="expression" dxfId="66" priority="65">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="expression" dxfId="45" priority="70">
+    <cfRule type="expression" dxfId="65" priority="84">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84:D84 A66:D75">
-    <cfRule type="expression" dxfId="44" priority="48">
+    <cfRule type="expression" dxfId="64" priority="62">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E23:E29">
-    <cfRule type="expression" dxfId="43" priority="47">
+    <cfRule type="expression" dxfId="63" priority="61">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30:E36">
-    <cfRule type="expression" dxfId="42" priority="46">
+    <cfRule type="expression" dxfId="62" priority="60">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E37:E45">
-    <cfRule type="expression" dxfId="41" priority="45">
+    <cfRule type="expression" dxfId="61" priority="59">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E46:E65">
-    <cfRule type="expression" dxfId="40" priority="44">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E66:E68 E84">
-    <cfRule type="expression" dxfId="39" priority="43">
+    <cfRule type="expression" dxfId="60" priority="58">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E66:E68 E84:E91">
+    <cfRule type="expression" dxfId="59" priority="57">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B56">
-    <cfRule type="expression" dxfId="38" priority="42">
+    <cfRule type="expression" dxfId="58" priority="56">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C56">
-    <cfRule type="expression" dxfId="37" priority="41">
+    <cfRule type="expression" dxfId="57" priority="55">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D56">
-    <cfRule type="expression" dxfId="36" priority="40">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B93:B94 B100:B101 B97:B98 B113:B116 B119:B120 B107 B122:B123 B104:B105">
-    <cfRule type="expression" dxfId="35" priority="39">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B92 B99 B106 B85 B121 B95:B96 B102:B103 B111:B112 B117:B118 B124">
-    <cfRule type="expression" dxfId="34" priority="38">
+    <cfRule type="expression" dxfId="56" priority="54">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B120:B123 B126:B127 B129:B130">
+    <cfRule type="expression" dxfId="55" priority="53">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B128 B118:B119 B124:B125 B131">
+    <cfRule type="expression" dxfId="54" priority="52">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B117">
+    <cfRule type="expression" dxfId="52" priority="50">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E92:E131">
+    <cfRule type="expression" dxfId="42" priority="40">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A117:A131">
+    <cfRule type="expression" dxfId="41" priority="39">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A76:D83">
+    <cfRule type="expression" dxfId="40" priority="38">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E76:E83">
+    <cfRule type="expression" dxfId="39" priority="37">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E69:E75">
+    <cfRule type="expression" dxfId="38" priority="35">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:A12">
+    <cfRule type="expression" dxfId="37" priority="31">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:D15">
+    <cfRule type="expression" dxfId="36" priority="30">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:A12">
+    <cfRule type="expression" dxfId="35" priority="29">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3:C15">
+    <cfRule type="expression" dxfId="34" priority="28">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:B5">
+    <cfRule type="expression" dxfId="33" priority="25">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6:B10">
+    <cfRule type="expression" dxfId="32" priority="23">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:B12">
+    <cfRule type="expression" dxfId="31" priority="21">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13:A15">
+    <cfRule type="expression" dxfId="30" priority="18">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13:A15">
+    <cfRule type="expression" dxfId="29" priority="17">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13:B15">
+    <cfRule type="expression" dxfId="28" priority="15">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B85">
+    <cfRule type="expression" dxfId="25" priority="13">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B86:B91">
-    <cfRule type="expression" dxfId="33" priority="37">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B108:B110">
-    <cfRule type="expression" dxfId="32" priority="36">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C85:C91">
-    <cfRule type="expression" dxfId="31" priority="35">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C92">
-    <cfRule type="expression" dxfId="30" priority="34">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C95">
-    <cfRule type="expression" dxfId="29" priority="33">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C98">
-    <cfRule type="expression" dxfId="28" priority="32">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C101">
-    <cfRule type="expression" dxfId="27" priority="31">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C93">
-    <cfRule type="expression" dxfId="26" priority="30">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C96">
-    <cfRule type="expression" dxfId="25" priority="29">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C99">
-    <cfRule type="expression" dxfId="24" priority="28">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C102">
-    <cfRule type="expression" dxfId="23" priority="27">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E85:E124">
-    <cfRule type="expression" dxfId="22" priority="26">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A85:A124">
-    <cfRule type="expression" dxfId="21" priority="25">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A76:D83">
-    <cfRule type="expression" dxfId="20" priority="24">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E76:E83">
-    <cfRule type="expression" dxfId="19" priority="23">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E69:E75">
-    <cfRule type="expression" dxfId="18" priority="21">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A3:A12">
-    <cfRule type="expression" dxfId="17" priority="17">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D3:D15">
-    <cfRule type="expression" dxfId="16" priority="16">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A3:A12">
-    <cfRule type="expression" dxfId="15" priority="15">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C15">
-    <cfRule type="expression" dxfId="14" priority="14">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B3:B5">
-    <cfRule type="expression" dxfId="11" priority="11">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6:B10">
-    <cfRule type="expression" dxfId="9" priority="9">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B11:B12">
-    <cfRule type="expression" dxfId="7" priority="7">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A13:A15">
-    <cfRule type="expression" dxfId="4" priority="4">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A13:A15">
-    <cfRule type="expression" dxfId="3" priority="3">
-      <formula>#REF!="SIN STOCK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13:B15">
+    <cfRule type="expression" dxfId="23" priority="12">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C85">
+    <cfRule type="expression" dxfId="21" priority="11">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C89">
+    <cfRule type="expression" dxfId="19" priority="10">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C86">
+    <cfRule type="expression" dxfId="17" priority="9">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C90">
+    <cfRule type="expression" dxfId="15" priority="8">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C91">
+    <cfRule type="expression" dxfId="13" priority="7">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C87:C88">
+    <cfRule type="expression" dxfId="11" priority="6">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D87:D91">
+    <cfRule type="expression" dxfId="9" priority="5">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D85:D86">
+    <cfRule type="expression" dxfId="7" priority="4">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A85:A91">
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A92:A116">
+    <cfRule type="expression" dxfId="3" priority="2">
+      <formula>#REF!="SIN STOCK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B92:D116">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>#REF!="SIN STOCK"</formula>
     </cfRule>
